--- a/plate3d/PLATE3D_SPLICE.xlsx
+++ b/plate3d/PLATE3D_SPLICE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="213">
   <si>
     <t>Section</t>
   </si>
@@ -597,13 +597,13 @@
     <t>The bolts, one row each. These are placed at the layout PARAM opens with; change a bolt count and the holes follow but these rows do not.</t>
   </si>
   <si>
-    <t>flange bolts - the shank, drawn through the pack</t>
+    <t>flange bolts - one row a quadrant, the counts from PARAM</t>
   </si>
   <si>
     <t>md.blt</t>
   </si>
   <si>
-    <t>web bolts</t>
+    <t>web bolts - the depth is one run, so two rows not four</t>
   </si>
   <si>
     <t>bo.f_1</t>
@@ -3295,7 +3295,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -5471,7 +5471,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
         <v>194</v>
       </c>
@@ -5500,8 +5500,45 @@
       <c r="I77" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J77" s="21">
+        <v>0</v>
+      </c>
+      <c r="K77" s="21">
+        <v>0</v>
+      </c>
+      <c r="L77" s="21">
+        <v>0</v>
+      </c>
+      <c r="M77" s="21">
+        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N77" s="21">
+        <v>0</v>
+      </c>
+      <c r="O77" s="21">
+        <v>0</v>
+      </c>
+      <c r="P77" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q77" s="21">
+        <v>0</v>
+      </c>
+      <c r="R77" s="21">
+        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S77" s="21">
+        <v>0</v>
+      </c>
+      <c r="T77" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B78" s="20" t="s">
         <v>172</v>
       </c>
@@ -5517,8 +5554,8 @@
         <v>35</v>
       </c>
       <c r="G78" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
+        <f>=-(PARAM!$G$28/2)</f>
+        <v>-50</v>
       </c>
       <c r="H78" s="21">
         <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
@@ -5527,8 +5564,45 @@
       <c r="I78" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J78" s="21">
+        <v>0</v>
+      </c>
+      <c r="K78" s="21">
+        <v>0</v>
+      </c>
+      <c r="L78" s="21">
+        <v>0</v>
+      </c>
+      <c r="M78" s="21">
+        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N78" s="21">
+        <v>0</v>
+      </c>
+      <c r="O78" s="21">
+        <v>0</v>
+      </c>
+      <c r="P78" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q78" s="21">
+        <v>0</v>
+      </c>
+      <c r="R78" s="21">
+        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S78" s="21">
+        <v>0</v>
+      </c>
+      <c r="T78" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
         <v>172</v>
       </c>
@@ -5540,12 +5614,12 @@
       </c>
       <c r="E79" s="21"/>
       <c r="F79" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
+        <f>=-(PARAM!$D$28/2)</f>
+        <v>-35</v>
       </c>
       <c r="G79" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
+        <f>=(PARAM!$G$28/2)</f>
+        <v>50</v>
       </c>
       <c r="H79" s="21">
         <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
@@ -5554,8 +5628,45 @@
       <c r="I79" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J79" s="21">
+        <v>0</v>
+      </c>
+      <c r="K79" s="21">
+        <v>0</v>
+      </c>
+      <c r="L79" s="21">
+        <v>0</v>
+      </c>
+      <c r="M79" s="21">
+        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N79" s="21">
+        <v>0</v>
+      </c>
+      <c r="O79" s="21">
+        <v>0</v>
+      </c>
+      <c r="P79" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q79" s="21">
+        <v>0</v>
+      </c>
+      <c r="R79" s="21">
+        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S79" s="21">
+        <v>0</v>
+      </c>
+      <c r="T79" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B80" s="20" t="s">
         <v>172</v>
       </c>
@@ -5567,12 +5678,12 @@
       </c>
       <c r="E80" s="21"/>
       <c r="F80" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
+        <f>=-(PARAM!$D$28/2)</f>
+        <v>-35</v>
       </c>
       <c r="G80" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
+        <f>=-(PARAM!$G$28/2)</f>
+        <v>-50</v>
       </c>
       <c r="H80" s="21">
         <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
@@ -5581,8 +5692,45 @@
       <c r="I80" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J80" s="21">
+        <v>0</v>
+      </c>
+      <c r="K80" s="21">
+        <v>0</v>
+      </c>
+      <c r="L80" s="21">
+        <v>0</v>
+      </c>
+      <c r="M80" s="21">
+        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N80" s="21">
+        <v>0</v>
+      </c>
+      <c r="O80" s="21">
+        <v>0</v>
+      </c>
+      <c r="P80" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q80" s="21">
+        <v>0</v>
+      </c>
+      <c r="R80" s="21">
+        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S80" s="21">
+        <v>0</v>
+      </c>
+      <c r="T80" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="20" t="s">
         <v>172</v>
       </c>
@@ -5594,22 +5742,59 @@
       </c>
       <c r="E81" s="21"/>
       <c r="F81" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
+        <f>=(PARAM!$D$28/2)</f>
+        <v>35</v>
       </c>
       <c r="G81" s="21">
         <f>=(PARAM!$G$28/2)</f>
         <v>50</v>
       </c>
       <c r="H81" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
+        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
+        <v>-177</v>
       </c>
       <c r="I81" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J81" s="21">
+        <v>0</v>
+      </c>
+      <c r="K81" s="21">
+        <v>0</v>
+      </c>
+      <c r="L81" s="21">
+        <v>0</v>
+      </c>
+      <c r="M81" s="21">
+        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N81" s="21">
+        <v>0</v>
+      </c>
+      <c r="O81" s="21">
+        <v>0</v>
+      </c>
+      <c r="P81" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q81" s="21">
+        <v>0</v>
+      </c>
+      <c r="R81" s="21">
+        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S81" s="21">
+        <v>0</v>
+      </c>
+      <c r="T81" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="20" t="s">
         <v>172</v>
       </c>
@@ -5621,22 +5806,59 @@
       </c>
       <c r="E82" s="21"/>
       <c r="F82" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
+        <f>=(PARAM!$D$28/2)</f>
+        <v>35</v>
       </c>
       <c r="G82" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
+        <f>=-(PARAM!$G$28/2)</f>
+        <v>-50</v>
       </c>
       <c r="H82" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
+        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
+        <v>-177</v>
       </c>
       <c r="I82" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J82" s="21">
+        <v>0</v>
+      </c>
+      <c r="K82" s="21">
+        <v>0</v>
+      </c>
+      <c r="L82" s="21">
+        <v>0</v>
+      </c>
+      <c r="M82" s="21">
+        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N82" s="21">
+        <v>0</v>
+      </c>
+      <c r="O82" s="21">
+        <v>0</v>
+      </c>
+      <c r="P82" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q82" s="21">
+        <v>0</v>
+      </c>
+      <c r="R82" s="21">
+        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S82" s="21">
+        <v>0</v>
+      </c>
+      <c r="T82" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B83" s="20" t="s">
         <v>172</v>
       </c>
@@ -5648,49 +5870,126 @@
       </c>
       <c r="E83" s="21"/>
       <c r="F83" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
+        <f>=-(PARAM!$D$28/2)</f>
+        <v>-35</v>
       </c>
       <c r="G83" s="21">
+        <f>=(PARAM!$G$28/2)</f>
+        <v>50</v>
+      </c>
+      <c r="H83" s="21">
+        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
+        <v>-177</v>
+      </c>
+      <c r="I83" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="J83" s="21">
+        <v>0</v>
+      </c>
+      <c r="K83" s="21">
+        <v>0</v>
+      </c>
+      <c r="L83" s="21">
+        <v>0</v>
+      </c>
+      <c r="M83" s="21">
+        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N83" s="21">
+        <v>0</v>
+      </c>
+      <c r="O83" s="21">
+        <v>0</v>
+      </c>
+      <c r="P83" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q83" s="21">
+        <v>0</v>
+      </c>
+      <c r="R83" s="21">
+        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S83" s="21">
+        <v>0</v>
+      </c>
+      <c r="T83" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B84" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21">
+        <f>=-(PARAM!$D$28/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="G84" s="21">
         <f>=-(PARAM!$G$28/2)</f>
         <v>-50</v>
       </c>
-      <c r="H83" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I83" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B84" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
-      </c>
-      <c r="G84" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
-      </c>
       <c r="H84" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
+        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
+        <v>-177</v>
       </c>
       <c r="I84" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J84" s="21">
+        <v>0</v>
+      </c>
+      <c r="K84" s="21">
+        <v>0</v>
+      </c>
+      <c r="L84" s="21">
+        <v>0</v>
+      </c>
+      <c r="M84" s="21">
+        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N84" s="21">
+        <v>0</v>
+      </c>
+      <c r="O84" s="21">
+        <v>0</v>
+      </c>
+      <c r="P84" s="21">
+        <f>=PARAM!$C$28/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q84" s="21">
+        <v>0</v>
+      </c>
+      <c r="R84" s="21">
+        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S84" s="21">
+        <v>0</v>
+      </c>
+      <c r="T84" s="21">
+        <f>=PARAM!$F$28/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
+        <v>196</v>
+      </c>
       <c r="B85" s="20" t="s">
         <v>172</v>
       </c>
@@ -5698,26 +5997,63 @@
         <v>195</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E85" s="21"/>
       <c r="F85" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
+        <f>=(PARAM!$D$29/2)</f>
+        <v>30</v>
       </c>
       <c r="G85" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
+        <f>=PARAM!$G$25/2</f>
+        <v>30</v>
       </c>
       <c r="H85" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
+        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
+        <v>-70</v>
       </c>
       <c r="I85" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="J85" s="21">
+        <v>0</v>
+      </c>
+      <c r="K85" s="21">
+        <v>0</v>
+      </c>
+      <c r="L85" s="21">
+        <v>0</v>
+      </c>
+      <c r="M85" s="21">
+        <f>=((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
+        <v>70</v>
+      </c>
+      <c r="N85" s="21">
+        <v>0</v>
+      </c>
+      <c r="O85" s="21">
+        <v>0</v>
+      </c>
+      <c r="P85" s="21">
+        <f>=PARAM!$C$29/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q85" s="21">
+        <v>0</v>
+      </c>
+      <c r="R85" s="21">
+        <v>0</v>
+      </c>
+      <c r="S85" s="21">
+        <f>=(PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1)</f>
+        <v>70</v>
+      </c>
+      <c r="T85" s="21">
+        <f>=PARAM!$F$29-1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B86" s="20" t="s">
         <v>172</v>
       </c>
@@ -5725,26 +6061,63 @@
         <v>195</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E86" s="21"/>
       <c r="F86" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
+        <f>=-(PARAM!$D$29/2)</f>
+        <v>-30</v>
       </c>
       <c r="G86" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
+        <f>=PARAM!$G$25/2</f>
+        <v>30</v>
       </c>
       <c r="H86" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
+        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
+        <v>-70</v>
       </c>
       <c r="I86" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="J86" s="21">
+        <v>0</v>
+      </c>
+      <c r="K86" s="21">
+        <v>0</v>
+      </c>
+      <c r="L86" s="21">
+        <v>0</v>
+      </c>
+      <c r="M86" s="21">
+        <f>=-((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
+        <v>-70</v>
+      </c>
+      <c r="N86" s="21">
+        <v>0</v>
+      </c>
+      <c r="O86" s="21">
+        <v>0</v>
+      </c>
+      <c r="P86" s="21">
+        <f>=PARAM!$C$29/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q86" s="21">
+        <v>0</v>
+      </c>
+      <c r="R86" s="21">
+        <v>0</v>
+      </c>
+      <c r="S86" s="21">
+        <f>=(PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1)</f>
+        <v>70</v>
+      </c>
+      <c r="T86" s="21">
+        <f>=PARAM!$F$29-1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="20" t="s">
         <v>172</v>
       </c>
@@ -5752,1231 +6125,310 @@
         <v>195</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E87" s="21"/>
-      <c r="F87" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G87" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H87" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I87" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B88" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C88" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B90" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F90" s="21">
+        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <v>-460</v>
+      </c>
+      <c r="G90" s="21">
+        <v>0</v>
+      </c>
+      <c r="H90" s="21">
+        <f>=(PARAM!$D$6/2-PARAM!$G$6/2)</f>
+        <v>142.5</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B91" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F91" s="21">
+        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <v>460</v>
+      </c>
+      <c r="G91" s="21">
+        <v>0</v>
+      </c>
+      <c r="H91" s="21">
+        <f>=(PARAM!$D$6/2-PARAM!$G$6/2)</f>
+        <v>142.5</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B92" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F92" s="21">
+        <v>0</v>
+      </c>
+      <c r="G92" s="21">
+        <v>0</v>
+      </c>
+      <c r="H92" s="21">
+        <f>=PARAM!$D$6/2+PARAM!$E$15/2</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B93" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="E93" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F93" s="21">
+        <v>0</v>
+      </c>
+      <c r="G93" s="21">
+        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
+        <v>77.5</v>
+      </c>
+      <c r="H93" s="21">
+        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2</f>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B94" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F94" s="21">
+        <v>0</v>
+      </c>
+      <c r="G94" s="21">
+        <v>0</v>
+      </c>
+      <c r="H94" s="21">
+        <f>=-(PARAM!$D$6/2+PARAM!$E$15/2)</f>
+        <v>-156</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B95" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C95" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D95" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F95" s="21">
+        <v>0</v>
+      </c>
+      <c r="G95" s="21">
+        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
+        <v>77.5</v>
+      </c>
+      <c r="H95" s="21">
+        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2)</f>
+        <v>-130</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B96" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F96" s="21">
+        <v>0</v>
+      </c>
+      <c r="G96" s="21">
+        <f>=PARAM!$F$6/2+PARAM!$E$17/2</f>
+        <v>10</v>
+      </c>
+      <c r="H96" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B97" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D97" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="D88" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E88" s="21"/>
-      <c r="F88" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G88" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
-      </c>
-      <c r="H88" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I88" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B89" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E89" s="21"/>
-      <c r="F89" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G89" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H89" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I89" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B90" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C90" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D90" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E90" s="21"/>
-      <c r="F90" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G90" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
-      </c>
-      <c r="H90" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I90" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B91" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C91" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D91" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E91" s="21"/>
-      <c r="F91" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G91" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H91" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I91" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B92" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C92" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D92" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G92" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
-      </c>
-      <c r="H92" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I92" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B93" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C93" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D93" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E93" s="21"/>
-      <c r="F93" s="21">
+      <c r="E97" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="F97" s="21">
         <f>=(PARAM!$D$28/2)</f>
         <v>35</v>
-      </c>
-      <c r="G93" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H93" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I93" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B94" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C94" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D94" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E94" s="21"/>
-      <c r="F94" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G94" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
-      </c>
-      <c r="H94" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I94" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B95" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C95" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D95" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E95" s="21"/>
-      <c r="F95" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G95" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H95" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I95" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B96" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C96" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D96" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E96" s="21"/>
-      <c r="F96" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G96" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
-      </c>
-      <c r="H96" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I96" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C97" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D97" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E97" s="21"/>
-      <c r="F97" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
       </c>
       <c r="G97" s="21">
         <f>=(PARAM!$G$28/2)</f>
         <v>50</v>
       </c>
       <c r="H97" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I97" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C98" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D98" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E98" s="21"/>
-      <c r="F98" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
-      </c>
-      <c r="G98" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
-      </c>
-      <c r="H98" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I98" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B99" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C99" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D99" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E99" s="21"/>
-      <c r="F99" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
-      </c>
-      <c r="G99" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H99" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I99" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B100" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C100" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D100" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E100" s="21"/>
-      <c r="F100" s="21">
-        <f>=(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>110</v>
-      </c>
-      <c r="G100" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
-      </c>
-      <c r="H100" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I100" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B101" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C101" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D101" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G101" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H101" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I101" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B102" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C102" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D102" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G102" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
-      </c>
-      <c r="H102" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I102" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C103" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D103" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G103" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H103" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I103" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B104" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C104" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D104" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E104" s="21"/>
-      <c r="F104" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G104" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
-      </c>
-      <c r="H104" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I104" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B105" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C105" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D105" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E105" s="21"/>
-      <c r="F105" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G105" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H105" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I105" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B106" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C106" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D106" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E106" s="21"/>
-      <c r="F106" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G106" s="21">
-        <f>=(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>105</v>
-      </c>
-      <c r="H106" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I106" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B107" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C107" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D107" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E107" s="21"/>
-      <c r="F107" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G107" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H107" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I107" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B108" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C108" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D108" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E108" s="21"/>
-      <c r="F108" s="21">
-        <f>=-(PARAM!$D$28/2+(PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-110</v>
-      </c>
-      <c r="G108" s="21">
-        <f>=-(PARAM!$G$28/2+(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-105</v>
-      </c>
-      <c r="H108" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I108" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B109" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C109" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D109" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E109" s="21"/>
-      <c r="F109" s="21">
-        <f>=(PARAM!$D$29/2)</f>
-        <v>30</v>
-      </c>
-      <c r="G109" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H109" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="I109" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B110" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C110" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D110" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E110" s="21"/>
-      <c r="F110" s="21">
-        <f>=(PARAM!$D$29/2)</f>
-        <v>30</v>
-      </c>
-      <c r="G110" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H110" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*1</f>
-        <v>0</v>
-      </c>
-      <c r="I110" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B111" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C111" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D111" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E111" s="21"/>
-      <c r="F111" s="21">
-        <f>=(PARAM!$D$29/2)</f>
-        <v>30</v>
-      </c>
-      <c r="G111" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H111" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*2</f>
-        <v>70</v>
-      </c>
-      <c r="I111" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B112" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C112" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D112" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E112" s="21"/>
-      <c r="F112" s="21">
-        <f>=(PARAM!$D$29/2+(PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>100</v>
-      </c>
-      <c r="G112" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H112" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="I112" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B113" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C113" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D113" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E113" s="21"/>
-      <c r="F113" s="21">
-        <f>=(PARAM!$D$29/2+(PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>100</v>
-      </c>
-      <c r="G113" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H113" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*1</f>
-        <v>0</v>
-      </c>
-      <c r="I113" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B114" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C114" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D114" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E114" s="21"/>
-      <c r="F114" s="21">
-        <f>=(PARAM!$D$29/2+(PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>100</v>
-      </c>
-      <c r="G114" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H114" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*2</f>
-        <v>70</v>
-      </c>
-      <c r="I114" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B115" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C115" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D115" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E115" s="21"/>
-      <c r="F115" s="21">
-        <f>=-(PARAM!$D$29/2)</f>
-        <v>-30</v>
-      </c>
-      <c r="G115" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H115" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="I115" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B116" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C116" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D116" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E116" s="21"/>
-      <c r="F116" s="21">
-        <f>=-(PARAM!$D$29/2)</f>
-        <v>-30</v>
-      </c>
-      <c r="G116" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H116" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*1</f>
-        <v>0</v>
-      </c>
-      <c r="I116" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B117" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C117" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D117" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E117" s="21"/>
-      <c r="F117" s="21">
-        <f>=-(PARAM!$D$29/2)</f>
-        <v>-30</v>
-      </c>
-      <c r="G117" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H117" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*2</f>
-        <v>70</v>
-      </c>
-      <c r="I117" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B118" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C118" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D118" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E118" s="21"/>
-      <c r="F118" s="21">
-        <f>=-(PARAM!$D$29/2+(PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>-100</v>
-      </c>
-      <c r="G118" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H118" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="I118" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B119" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C119" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D119" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E119" s="21"/>
-      <c r="F119" s="21">
-        <f>=-(PARAM!$D$29/2+(PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>-100</v>
-      </c>
-      <c r="G119" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H119" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*1</f>
-        <v>0</v>
-      </c>
-      <c r="I119" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B120" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C120" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D120" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E120" s="21"/>
-      <c r="F120" s="21">
-        <f>=-(PARAM!$D$29/2+(PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>-100</v>
-      </c>
-      <c r="G120" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H120" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)+((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1))*2</f>
-        <v>70</v>
-      </c>
-      <c r="I120" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B121" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C121" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D121" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="E121" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="F121" s="21" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="16" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B124" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C124" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D124" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="E124" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F124" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
-        <v>-460</v>
-      </c>
-      <c r="G124" s="21">
-        <v>0</v>
-      </c>
-      <c r="H124" s="21">
-        <f>=(PARAM!$D$6/2-PARAM!$G$6/2)</f>
-        <v>142.5</v>
-      </c>
-    </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B125" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C125" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D125" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="E125" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F125" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
-        <v>460</v>
-      </c>
-      <c r="G125" s="21">
-        <v>0</v>
-      </c>
-      <c r="H125" s="21">
-        <f>=(PARAM!$D$6/2-PARAM!$G$6/2)</f>
-        <v>142.5</v>
-      </c>
-    </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B126" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C126" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D126" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="E126" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F126" s="21">
-        <v>0</v>
-      </c>
-      <c r="G126" s="21">
-        <v>0</v>
-      </c>
-      <c r="H126" s="21">
-        <f>=PARAM!$D$6/2+PARAM!$E$15/2</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B127" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C127" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D127" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="E127" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F127" s="21">
-        <v>0</v>
-      </c>
-      <c r="G127" s="21">
-        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
-        <v>77.5</v>
-      </c>
-      <c r="H127" s="21">
-        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2</f>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B128" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C128" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D128" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E128" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F128" s="21">
-        <v>0</v>
-      </c>
-      <c r="G128" s="21">
-        <v>0</v>
-      </c>
-      <c r="H128" s="21">
-        <f>=-(PARAM!$D$6/2+PARAM!$E$15/2)</f>
-        <v>-156</v>
-      </c>
-    </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B129" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C129" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D129" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E129" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F129" s="21">
-        <v>0</v>
-      </c>
-      <c r="G129" s="21">
-        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
-        <v>77.5</v>
-      </c>
-      <c r="H129" s="21">
-        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2)</f>
-        <v>-130</v>
-      </c>
-    </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B130" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C130" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D130" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="E130" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F130" s="21">
-        <v>0</v>
-      </c>
-      <c r="G130" s="21">
-        <f>=PARAM!$F$6/2+PARAM!$E$17/2</f>
-        <v>10</v>
-      </c>
-      <c r="H130" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B131" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C131" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="D131" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E131" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="F131" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G131" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H131" s="21">
         <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
         <v>110</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="16" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="16" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="16" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" s="20" t="s">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C134" s="21" t="s">
+      <c r="C100" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="D134" s="21" t="s">
+      <c r="D100" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="E134" s="21" t="s">
+      <c r="E100" s="21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B135" s="20" t="s">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B101" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C135" s="21" t="s">
+      <c r="C101" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="D135" s="21" t="s">
+      <c r="D101" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="E135" s="21" t="s">
+      <c r="E101" s="21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B136" s="20" t="s">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B102" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C136" s="21" t="s">
+      <c r="C102" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="D136" s="21" t="s">
+      <c r="D102" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="E136" s="21" t="s">
+      <c r="E102" s="21" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B137" s="20" t="s">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B103" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C137" s="21" t="s">
+      <c r="C103" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D137" s="21" t="s">
+      <c r="D103" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="E137" s="21" t="s">
+      <c r="E103" s="21" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B138" s="20" t="s">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B104" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C138" s="21" t="s">
+      <c r="C104" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="D138" s="21" t="s">
+      <c r="D104" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="E138" s="21" t="s">
+      <c r="E104" s="21" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="16" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B140" s="20" t="s">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="20" t="s">
         <v>212</v>
       </c>
     </row>

--- a/plate3d/PLATE3D_SPLICE.xlsx
+++ b/plate3d/PLATE3D_SPLICE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="212">
   <si>
     <t>Section</t>
   </si>
@@ -216,7 +216,7 @@
     <t>Fill in the blue cells. Everything else follows — the input tab is written from this one, and nothing on it needs touching.</t>
   </si>
   <si>
-    <t xml:space="preserve">  1.  MEMBERS AND JOINT</t>
+    <t xml:space="preserve">  1.  MEMBER AND JOINT</t>
   </si>
   <si>
     <t>pick a section and the sizes fill themselves in</t>
@@ -234,16 +234,13 @@
     <t>Length</t>
   </si>
   <si>
-    <t>Left member</t>
-  </si>
-  <si>
-    <t>Right member</t>
+    <t>Member</t>
   </si>
   <si>
     <t>Joint gap</t>
   </si>
   <si>
-    <t>The two members are drawn as three plates each — top flange, bottom flange, web — because a rolled section cannot be drilled: a CUT on a SECT cuts its whole length. Root fillets are not modelled.</t>
+    <t>One section, spliced to itself — both sides of the joint are the same member, so there is one row to fill in and Length is the reach of each side. Each side is drawn as three plates — top flange, bottom flange, web — because a rolled section cannot be drilled: a CUT on a SECT cuts its whole length. Root fillets are modelled as eight fillet strips.</t>
   </si>
   <si>
     <t>checked for you</t>
@@ -363,7 +360,7 @@
     <t>the same drawings, to the sizes above</t>
   </si>
   <si>
-    <t>The two members and the gap between them, seen from above</t>
+    <t>The joint in plan — one section either side, and the gap between</t>
   </si>
   <si>
     <t>The section at the joint — which plate goes where</t>
@@ -384,7 +381,7 @@
     <t>ZUP</t>
   </si>
   <si>
-    <t>the bolt hole - PARAM row 25, the hole column, not the shank</t>
+    <t>the bolt hole - PARAM row 24, the hole column, not the shank</t>
   </si>
   <si>
     <t>HOLE</t>
@@ -877,7 +874,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>41999</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7905750" cy="3952875"/>
@@ -916,7 +913,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>41999</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6667500" cy="5090388"/>
@@ -955,7 +952,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>41999</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8572500" cy="6540972"/>
@@ -994,7 +991,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>41999</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8382000" cy="5584902"/>
@@ -2726,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J132"/>
+  <dimension ref="B1:J131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2826,134 +2823,119 @@
         <v>900</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="15">
-        <f>IFERROR(VLOOKUP($C$7,SECT!$A:$G,2,FALSE),"")</f>
-        <v>300</v>
-      </c>
-      <c r="E7" s="15">
-        <f>IFERROR(VLOOKUP($C$7,SECT!$A:$G,3,FALSE),"")</f>
-        <v>300</v>
-      </c>
-      <c r="F7" s="15">
-        <f>IFERROR(VLOOKUP($C$7,SECT!$A:$G,4,FALSE),"")</f>
-        <v>10</v>
-      </c>
-      <c r="G7" s="15">
-        <f>IFERROR(VLOOKUP($C$7,SECT!$A:$G,5,FALSE),"")</f>
-        <v>15</v>
-      </c>
-      <c r="H7" s="15">
-        <f>IFERROR(VLOOKUP($C$7,SECT!$A:$G,6,FALSE),"")</f>
-        <v>18</v>
-      </c>
-      <c r="I7" s="15">
-        <f>IFERROR(VLOOKUP($C$7,SECT!$A:$G,7,FALSE),"")</f>
-        <v>94</v>
-      </c>
-      <c r="J7" s="14">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="C7" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="17">
+      <c r="D10" s="17">
         <f>=PARAM!$D$6-2*PARAM!$G$6</f>
         <v>270</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E10" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="17">
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="17">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
-        <v>460</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
+      <c r="D13" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>85</v>
+      </c>
+      <c r="C14" s="14">
+        <v>280</v>
+      </c>
+      <c r="D14" s="14">
+        <v>300</v>
+      </c>
+      <c r="E14" s="14">
+        <v>12</v>
+      </c>
+      <c r="F14" s="19">
+        <v>1</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" s="14">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="D15" s="14">
         <v>300</v>
       </c>
       <c r="E15" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F15" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2961,10 +2943,10 @@
         <v>88</v>
       </c>
       <c r="C16" s="14">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="D16" s="14">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E16" s="14">
         <v>10</v>
@@ -2973,7 +2955,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2981,10 +2963,10 @@
         <v>89</v>
       </c>
       <c r="C17" s="14">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="D17" s="14">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E17" s="14">
         <v>10</v>
@@ -2993,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -3001,131 +2983,134 @@
         <v>90</v>
       </c>
       <c r="C18" s="14">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="D18" s="14">
         <v>300</v>
       </c>
       <c r="E18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F18" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="14">
-        <v>280</v>
-      </c>
-      <c r="D19" s="14">
-        <v>300</v>
-      </c>
-      <c r="E19" s="14">
-        <v>12</v>
-      </c>
-      <c r="F19" s="19">
-        <v>1</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="18" t="s">
+      <c r="D20" s="17">
+        <f>=ROUND((PARAM!$C$14*PARAM!$D$14*PARAM!$E$14*2+PARAM!$C$15*PARAM!$D$15*PARAM!$E$15*4+PARAM!$C$16*PARAM!$D$16*PARAM!$E$16*2)*7.85/1000000,1)</f>
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="17">
-        <f>=ROUND((PARAM!$C$15*PARAM!$D$15*PARAM!$E$15*2+PARAM!$C$16*PARAM!$D$16*PARAM!$E$16*4+PARAM!$C$17*PARAM!$D$17*PARAM!$E$17*2)*7.85/1000000,1)</f>
-        <v>35.9</v>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="D23" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="B24" s="13" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="13" t="s">
+      <c r="C24" s="14">
+        <v>22</v>
+      </c>
+      <c r="D24" s="14">
+        <v>24</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="14">
-        <v>22</v>
-      </c>
-      <c r="D25" s="14">
-        <v>24</v>
-      </c>
-      <c r="E25" s="14" t="s">
+      <c r="F24" s="14">
+        <f>PARAM!$E$14+PARAM!$G$6+PARAM!$E$15+30</f>
+        <v>67</v>
+      </c>
+      <c r="G24" s="14">
+        <f>PARAM!$F$6+2*PARAM!$E$16+30</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="14">
-        <f>PARAM!$E$15+PARAM!$G$6+PARAM!$E$16+30</f>
-        <v>67</v>
-      </c>
-      <c r="G25" s="14">
-        <f>PARAM!$F$6+2*PARAM!$E$17+30</f>
-        <v>60</v>
+      <c r="C26" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="12" t="s">
+      <c r="B27" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>105</v>
+      <c r="C27" s="14">
+        <v>4</v>
+      </c>
+      <c r="D27" s="14">
+        <v>70</v>
+      </c>
+      <c r="E27" s="14">
+        <v>40</v>
+      </c>
+      <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>100</v>
+      </c>
+      <c r="H27" s="14">
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
@@ -3136,19 +3121,19 @@
         <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E28" s="14">
         <v>40</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H28" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
@@ -3159,131 +3144,108 @@
         <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E29" s="14">
         <v>40</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29" s="14">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="14">
-        <v>4</v>
-      </c>
-      <c r="D30" s="14">
-        <v>70</v>
-      </c>
-      <c r="E30" s="14">
-        <v>40</v>
-      </c>
-      <c r="F30" s="14">
-        <v>4</v>
-      </c>
-      <c r="G30" s="14">
-        <v>100</v>
-      </c>
-      <c r="H30" s="14">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="16" t="s">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="18" t="s">
+      <c r="D31" s="17" t="str">
+        <f>=ROUND((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1),1)&amp;" / "&amp;ROUND((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1),1)</f>
+        <v>75 / 55</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="17" t="str">
-        <f>=ROUND((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1),1)&amp;" / "&amp;ROUND((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1),1)</f>
-        <v>75 / 55</v>
-      </c>
-      <c r="E32" s="18" t="s">
+      <c r="F31" s="17" t="str">
+        <f>=ROUND((PARAM!$D$16/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1),1)&amp;" / "&amp;ROUND((PARAM!$C$16-2*PARAM!$H$28-PARAM!$G$28)/(PARAM!$F$28-1),1)</f>
+        <v>70 / 70</v>
+      </c>
+      <c r="G31" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="17" t="str">
-        <f>=ROUND((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1),1)&amp;" / "&amp;ROUND((PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1),1)</f>
-        <v>70 / 70</v>
-      </c>
-      <c r="G32" s="18" t="s">
+      <c r="H31" s="17">
+        <f>=PARAM!$C$27*PARAM!$F$27+PARAM!$C$29*PARAM!$F$29+PARAM!$C$28*PARAM!$F$28</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="H32" s="17">
-        <f>=PARAM!$C$28*PARAM!$F$28+PARAM!$C$30*PARAM!$F$30+PARAM!$C$29*PARAM!$F$29</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
+      <c r="C34" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="s">
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" s="13" t="s">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B93" s="13" t="s">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="13" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B132" s="13" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B30:J30"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" showErrorMessage="1" error="Pick one from the SECT tab." sqref="C6:C7">
+    <dataValidation type="list" showErrorMessage="1" error="Pick one from the SECT tab." sqref="C6">
       <formula1>SECT!$A$2:$A$59</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E25">
+    <dataValidation type="list" sqref="E24">
       <formula1>"F8T,F10T,F13T"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G15:G19">
+    <dataValidation type="list" sqref="G14:G18">
       <formula1>"SS275,SM355,SM420,SM460,SM490"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3306,15 +3268,15 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>121</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -3324,40 +3286,40 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="D4" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="E4" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>127</v>
-      </c>
       <c r="F4" s="21">
-        <f>=PARAM!$D$25</f>
+        <f>=PARAM!$D$24</f>
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>129</v>
-      </c>
       <c r="D5" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>126</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>127</v>
       </c>
       <c r="F5" s="21">
         <f>=2*PARAM!$H$6</f>
@@ -3371,21 +3333,21 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>133</v>
-      </c>
       <c r="D8" s="21" t="str">
-        <f>=PARAM!$G$15</f>
+        <f>=PARAM!$G$14</f>
         <v>SM355</v>
       </c>
       <c r="E8" s="21">
@@ -3393,10 +3355,10 @@
         <v>15</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H8" s="21">
         <f>=PARAM!$J$6</f>
@@ -3409,16 +3371,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="D9" s="21" t="str">
-        <f>=PARAM!$G$15</f>
+        <f>=PARAM!$G$14</f>
         <v>SM355</v>
       </c>
       <c r="E9" s="21">
@@ -3426,10 +3388,10 @@
         <v>15</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="21">
         <f>=PARAM!$J$6</f>
@@ -3442,16 +3404,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>138</v>
-      </c>
       <c r="D10" s="21" t="str">
-        <f>=PARAM!$G$15</f>
+        <f>=PARAM!$G$14</f>
         <v>SM355</v>
       </c>
       <c r="E10" s="21">
@@ -3459,10 +3421,10 @@
         <v>10</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H10" s="21">
         <f>=PARAM!$J$6</f>
@@ -3475,16 +3437,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>140</v>
-      </c>
       <c r="D11" s="21" t="str">
-        <f>=PARAM!$G$15</f>
+        <f>=PARAM!$G$14</f>
         <v>SM355</v>
       </c>
       <c r="E11" s="21">
@@ -3492,10 +3454,10 @@
         <v>900</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H11" s="21">
         <f>=PARAM!$H$6</f>
@@ -3508,166 +3470,166 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="21" t="s">
+      <c r="D12" s="21" t="str">
+        <f>=PARAM!$G$14</f>
+        <v>SM355</v>
+      </c>
+      <c r="E12" s="21">
+        <f>=PARAM!$E$14</f>
+        <v>12</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="21">
+        <f>=PARAM!$D$14</f>
+        <v>300</v>
+      </c>
+      <c r="I12" s="21">
+        <f>=PARAM!$C$14</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="21" t="str">
+      <c r="B13" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="21" t="str">
         <f>=PARAM!$G$15</f>
         <v>SM355</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E13" s="21">
         <f>=PARAM!$E$15</f>
-        <v>12</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H12" s="21">
+        <v>10</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="21">
         <f>=PARAM!$D$15</f>
         <v>300</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I13" s="21">
         <f>=PARAM!$C$15</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="21" t="str">
+      <c r="B14" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="21" t="str">
         <f>=PARAM!$G$16</f>
         <v>SM355</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E14" s="21">
         <f>=PARAM!$E$16</f>
         <v>10</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H13" s="21">
+      <c r="F14" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="21">
         <f>=PARAM!$D$16</f>
-        <v>300</v>
-      </c>
-      <c r="I13" s="21">
+        <v>280</v>
+      </c>
+      <c r="I14" s="21">
         <f>=PARAM!$C$16</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="21" t="str">
+      <c r="B15" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="21" t="str">
         <f>=PARAM!$G$17</f>
         <v>SM355</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E15" s="21">
         <f>=PARAM!$E$17</f>
         <v>10</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H14" s="21">
+      <c r="F15" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="21">
         <f>=PARAM!$D$17</f>
-        <v>280</v>
-      </c>
-      <c r="I14" s="21">
+        <v>300</v>
+      </c>
+      <c r="I15" s="21">
         <f>=PARAM!$C$17</f>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="21" t="str">
+      <c r="B16" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="21" t="str">
         <f>=PARAM!$G$18</f>
         <v>SM355</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E16" s="21">
         <f>=PARAM!$E$18</f>
-        <v>10</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H15" s="21">
+        <v>12</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="21">
         <f>=PARAM!$D$18</f>
         <v>300</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I16" s="21">
         <f>=PARAM!$C$18</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="21" t="str">
-        <f>=PARAM!$G$19</f>
-        <v>SM355</v>
-      </c>
-      <c r="E16" s="21">
-        <f>=PARAM!$E$19</f>
-        <v>12</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H16" s="21">
-        <f>=PARAM!$D$19</f>
-        <v>300</v>
-      </c>
-      <c r="I16" s="21">
-        <f>=PARAM!$C$19</f>
         <v>280</v>
       </c>
     </row>
@@ -3678,50 +3640,50 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="C19" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="D19" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>155</v>
-      </c>
       <c r="E19" s="21">
-        <f>=PARAM!$C$25</f>
+        <f>=PARAM!$C$24</f>
         <v>22</v>
       </c>
       <c r="F19" s="21">
-        <f>=PARAM!$F$25</f>
+        <f>=PARAM!$F$24</f>
         <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>157</v>
-      </c>
       <c r="D20" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E20" s="21">
-        <f>=PARAM!$C$25</f>
+        <f>=PARAM!$C$24</f>
         <v>22</v>
       </c>
       <c r="F20" s="21">
-        <f>=PARAM!$G$25</f>
+        <f>=PARAM!$G$24</f>
         <v>60</v>
       </c>
     </row>
@@ -3732,773 +3694,773 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="C23" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="E23" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="H23" s="21">
+        <v>0</v>
+      </c>
+      <c r="I23" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="21">
+        <v>0</v>
+      </c>
+      <c r="K23" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="L23" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="E24" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="H24" s="21">
+        <v>0</v>
+      </c>
+      <c r="I24" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J24" s="21">
+        <v>0</v>
+      </c>
+      <c r="K24" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="L24" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="E25" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0</v>
+      </c>
+      <c r="I25" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J25" s="21">
+        <v>0</v>
+      </c>
+      <c r="K25" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="L25" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="E26" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H26" s="21">
+        <v>0</v>
+      </c>
+      <c r="I26" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J26" s="21">
+        <v>0</v>
+      </c>
+      <c r="K26" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="L26" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="B27" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="E27" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="H27" s="21">
+        <v>0</v>
+      </c>
+      <c r="I27" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="21">
+        <v>0</v>
+      </c>
+      <c r="K27" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="L27" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="E28" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0</v>
+      </c>
+      <c r="I28" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J28" s="21">
+        <v>0</v>
+      </c>
+      <c r="K28" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="L28" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="E29" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H29" s="21">
+        <v>0</v>
+      </c>
+      <c r="I29" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J29" s="21">
+        <v>0</v>
+      </c>
+      <c r="K29" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="L29" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="E30" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H30" s="21">
+        <v>0</v>
+      </c>
+      <c r="I30" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="21">
+        <v>0</v>
+      </c>
+      <c r="K30" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="L30" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="E31" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
+        <v>-27.5</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="H31" s="21">
+        <v>0</v>
+      </c>
+      <c r="I31" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J31" s="21">
+        <v>0</v>
+      </c>
+      <c r="K31" s="21">
+        <f>=(PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="L31" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="E32" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
+        <v>-27.5</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H32" s="21">
+        <v>0</v>
+      </c>
+      <c r="I32" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J32" s="21">
+        <v>0</v>
+      </c>
+      <c r="K32" s="21">
+        <f>=(PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="L32" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="E33" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
+        <v>-27.5</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="H33" s="21">
+        <v>0</v>
+      </c>
+      <c r="I33" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J33" s="21">
+        <v>0</v>
+      </c>
+      <c r="K33" s="21">
+        <f>=(PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="L33" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="E34" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
+        <v>-27.5</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H34" s="21">
+        <v>0</v>
+      </c>
+      <c r="I34" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J34" s="21">
+        <v>0</v>
+      </c>
+      <c r="K34" s="21">
+        <f>=(PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="L34" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" s="21">
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2-PARAM!$D$27/2</f>
+        <v>425</v>
+      </c>
+      <c r="E35" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H35" s="21">
+        <v>0</v>
+      </c>
+      <c r="I35" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J35" s="21">
+        <v>0</v>
+      </c>
+      <c r="K35" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="L35" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="21">
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2-PARAM!$D$27/2</f>
+        <v>425</v>
+      </c>
+      <c r="E36" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G36" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H36" s="21">
+        <v>0</v>
+      </c>
+      <c r="I36" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J36" s="21">
+        <v>0</v>
+      </c>
+      <c r="K36" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="L36" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" s="21">
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2-PARAM!$D$27/2</f>
+        <v>425</v>
+      </c>
+      <c r="E37" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H37" s="21">
+        <v>0</v>
+      </c>
+      <c r="I37" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J37" s="21">
+        <v>0</v>
+      </c>
+      <c r="K37" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="L37" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="21">
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2-PARAM!$D$27/2</f>
+        <v>425</v>
+      </c>
+      <c r="E38" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="H38" s="21">
+        <v>0</v>
+      </c>
+      <c r="I38" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="J38" s="21">
+        <v>0</v>
+      </c>
+      <c r="K38" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="L38" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39" s="21">
         <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="E23" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G23" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="H23" s="21">
-        <v>0</v>
-      </c>
-      <c r="I23" s="21">
+        <v>30</v>
+      </c>
+      <c r="E39" s="21">
+        <f>=-(PARAM!$C$16/2-PARAM!$H$28)</f>
+        <v>-70</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" s="21">
+        <f>=((PARAM!$D$16/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>70</v>
+      </c>
+      <c r="H39" s="21">
+        <v>0</v>
+      </c>
+      <c r="I39" s="21">
         <f>=PARAM!$C$28/2-1</f>
         <v>1</v>
       </c>
-      <c r="J23" s="21">
-        <v>0</v>
-      </c>
-      <c r="K23" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="L23" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D24" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="E24" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="H24" s="21">
-        <v>0</v>
-      </c>
-      <c r="I24" s="21">
+      <c r="J39" s="21">
+        <v>0</v>
+      </c>
+      <c r="K39" s="21">
+        <f>=(PARAM!$C$16-2*PARAM!$H$28-PARAM!$G$28)/(PARAM!$F$28-1)</f>
+        <v>70</v>
+      </c>
+      <c r="L39" s="21">
+        <f>=PARAM!$F$28-1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="21">
+        <f>=-(PARAM!$D$28/2)</f>
+        <v>-30</v>
+      </c>
+      <c r="E40" s="21">
+        <f>=-(PARAM!$C$16/2-PARAM!$H$28)</f>
+        <v>-70</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G40" s="21">
+        <f>=-((PARAM!$D$16/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>-70</v>
+      </c>
+      <c r="H40" s="21">
+        <v>0</v>
+      </c>
+      <c r="I40" s="21">
         <f>=PARAM!$C$28/2-1</f>
         <v>1</v>
       </c>
-      <c r="J24" s="21">
-        <v>0</v>
-      </c>
-      <c r="K24" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="L24" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D25" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="E25" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G25" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H25" s="21">
-        <v>0</v>
-      </c>
-      <c r="I25" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J25" s="21">
-        <v>0</v>
-      </c>
-      <c r="K25" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="L25" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D26" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="E26" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H26" s="21">
-        <v>0</v>
-      </c>
-      <c r="I26" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J26" s="21">
-        <v>0</v>
-      </c>
-      <c r="K26" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="L26" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D27" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="E27" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G27" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="H27" s="21">
-        <v>0</v>
-      </c>
-      <c r="I27" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J27" s="21">
-        <v>0</v>
-      </c>
-      <c r="K27" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="L27" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="E28" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G28" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="H28" s="21">
-        <v>0</v>
-      </c>
-      <c r="I28" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J28" s="21">
-        <v>0</v>
-      </c>
-      <c r="K28" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="L28" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D29" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="E29" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G29" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H29" s="21">
-        <v>0</v>
-      </c>
-      <c r="I29" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J29" s="21">
-        <v>0</v>
-      </c>
-      <c r="K29" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="L29" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="E30" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H30" s="21">
-        <v>0</v>
-      </c>
-      <c r="I30" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J30" s="21">
-        <v>0</v>
-      </c>
-      <c r="K30" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="L30" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="E31" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
-        <v>-27.5</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G31" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="H31" s="21">
-        <v>0</v>
-      </c>
-      <c r="I31" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J31" s="21">
-        <v>0</v>
-      </c>
-      <c r="K31" s="21">
-        <f>=(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1)</f>
-        <v>55</v>
-      </c>
-      <c r="L31" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="E32" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
-        <v>-27.5</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G32" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H32" s="21">
-        <v>0</v>
-      </c>
-      <c r="I32" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J32" s="21">
-        <v>0</v>
-      </c>
-      <c r="K32" s="21">
-        <f>=(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1)</f>
-        <v>55</v>
-      </c>
-      <c r="L32" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="E33" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
-        <v>-27.5</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G33" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="H33" s="21">
-        <v>0</v>
-      </c>
-      <c r="I33" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J33" s="21">
-        <v>0</v>
-      </c>
-      <c r="K33" s="21">
-        <f>=(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1)</f>
-        <v>55</v>
-      </c>
-      <c r="L33" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="E34" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
-        <v>-27.5</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G34" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H34" s="21">
-        <v>0</v>
-      </c>
-      <c r="I34" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J34" s="21">
-        <v>0</v>
-      </c>
-      <c r="K34" s="21">
-        <f>=(PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1)</f>
-        <v>55</v>
-      </c>
-      <c r="L34" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2-PARAM!$D$28/2</f>
-        <v>425</v>
-      </c>
-      <c r="E35" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G35" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H35" s="21">
-        <v>0</v>
-      </c>
-      <c r="I35" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J35" s="21">
-        <v>0</v>
-      </c>
-      <c r="K35" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="L35" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2-PARAM!$D$28/2</f>
-        <v>425</v>
-      </c>
-      <c r="E36" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G36" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H36" s="21">
-        <v>0</v>
-      </c>
-      <c r="I36" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J36" s="21">
-        <v>0</v>
-      </c>
-      <c r="K36" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="L36" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="D37" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2-PARAM!$D$28/2</f>
-        <v>425</v>
-      </c>
-      <c r="E37" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G37" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H37" s="21">
-        <v>0</v>
-      </c>
-      <c r="I37" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J37" s="21">
-        <v>0</v>
-      </c>
-      <c r="K37" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="L37" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2-PARAM!$D$28/2</f>
-        <v>425</v>
-      </c>
-      <c r="E38" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G38" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="H38" s="21">
-        <v>0</v>
-      </c>
-      <c r="I38" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J38" s="21">
-        <v>0</v>
-      </c>
-      <c r="K38" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="L38" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="21">
-        <f>=(PARAM!$D$29/2)</f>
-        <v>30</v>
-      </c>
-      <c r="E39" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G39" s="21">
-        <f>=((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
+      <c r="J40" s="21">
+        <v>0</v>
+      </c>
+      <c r="K40" s="21">
+        <f>=(PARAM!$C$16-2*PARAM!$H$28-PARAM!$G$28)/(PARAM!$F$28-1)</f>
         <v>70</v>
       </c>
-      <c r="H39" s="21">
-        <v>0</v>
-      </c>
-      <c r="I39" s="21">
-        <f>=PARAM!$C$29/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J39" s="21">
-        <v>0</v>
-      </c>
-      <c r="K39" s="21">
-        <f>=(PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1)</f>
-        <v>70</v>
-      </c>
-      <c r="L39" s="21">
-        <f>=PARAM!$F$29-1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D40" s="21">
-        <f>=-(PARAM!$D$29/2)</f>
-        <v>-30</v>
-      </c>
-      <c r="E40" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G40" s="21">
-        <f>=-((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>-70</v>
-      </c>
-      <c r="H40" s="21">
-        <v>0</v>
-      </c>
-      <c r="I40" s="21">
-        <f>=PARAM!$C$29/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="J40" s="21">
-        <v>0</v>
-      </c>
-      <c r="K40" s="21">
-        <f>=(PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1)</f>
-        <v>70</v>
-      </c>
       <c r="L40" s="21">
-        <f>=PARAM!$F$29-1</f>
+        <f>=PARAM!$F$28-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D41" s="21">
         <f>=PARAM!$H$6/2</f>
@@ -4509,50 +4471,50 @@
         <v>-9</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2-PARAM!$D$29/2-((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))*(PARAM!$C$29/2-1)</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2-PARAM!$D$28/2-((PARAM!$D$16/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))*(PARAM!$C$28/2-1)</f>
         <v>360</v>
       </c>
       <c r="E42" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
+        <f>=-(PARAM!$C$16/2-PARAM!$H$28)</f>
         <v>-70</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G42" s="21">
-        <f>=(PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1)</f>
+        <f>=(PARAM!$D$16/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1)</f>
         <v>70</v>
       </c>
       <c r="H42" s="21">
         <v>0</v>
       </c>
       <c r="I42" s="21">
-        <f>=PARAM!$C$29/2-1</f>
+        <f>=PARAM!$C$28/2-1</f>
         <v>1</v>
       </c>
       <c r="J42" s="21">
         <v>0</v>
       </c>
       <c r="K42" s="21">
-        <f>=(PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1)</f>
+        <f>=(PARAM!$C$16-2*PARAM!$H$28-PARAM!$G$28)/(PARAM!$F$28-1)</f>
         <v>70</v>
       </c>
       <c r="L42" s="21">
-        <f>=PARAM!$F$29-1</f>
+        <f>=PARAM!$F$28-1</f>
         <v>2</v>
       </c>
     </row>
@@ -4563,32 +4525,32 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="C46" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C46" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D46" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F46" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G46" s="21">
@@ -4599,7 +4561,7 @@
         <v>142.5</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J46" s="21"/>
       <c r="K46" s="21"/>
@@ -4607,19 +4569,19 @@
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C47" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D47" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F47" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G47" s="21">
@@ -4630,7 +4592,7 @@
         <v>-142.5</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J47" s="21"/>
       <c r="K47" s="21"/>
@@ -4638,19 +4600,19 @@
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D48" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F48" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G48" s="21">
@@ -4660,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J48" s="21"/>
       <c r="K48" s="21"/>
@@ -4668,19 +4630,19 @@
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C49" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D49" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F49" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G49" s="21">
@@ -4692,7 +4654,7 @@
         <v>126</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J49" s="21">
         <v>0</v>
@@ -4706,19 +4668,19 @@
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C50" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D50" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F50" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G50" s="21">
@@ -4730,7 +4692,7 @@
         <v>126</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J50" s="21">
         <v>270</v>
@@ -4744,19 +4706,19 @@
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C51" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D51" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F51" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G51" s="21">
@@ -4768,7 +4730,7 @@
         <v>-126</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J51" s="21">
         <v>90</v>
@@ -4782,19 +4744,19 @@
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C52" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D52" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F52" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G52" s="21">
@@ -4806,7 +4768,7 @@
         <v>-126</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J52" s="21">
         <v>180</v>
@@ -4820,39 +4782,39 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C53" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D53" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="B54" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>179</v>
-      </c>
       <c r="D54" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F54" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G54" s="21">
@@ -4863,7 +4825,7 @@
         <v>142.5</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J54" s="21">
         <v>0</v>
@@ -4877,19 +4839,19 @@
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F55" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G55" s="21">
@@ -4900,7 +4862,7 @@
         <v>-142.5</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J55" s="21">
         <v>0</v>
@@ -4914,19 +4876,19 @@
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F56" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G56" s="21">
@@ -4936,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J56" s="21">
         <v>0</v>
@@ -4950,19 +4912,19 @@
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F57" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G57" s="21">
@@ -4974,7 +4936,7 @@
         <v>126</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J57" s="21">
         <v>0</v>
@@ -4988,19 +4950,19 @@
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F58" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G58" s="21">
@@ -5012,7 +4974,7 @@
         <v>126</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J58" s="21">
         <v>270</v>
@@ -5026,19 +4988,19 @@
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F59" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G59" s="21">
@@ -5050,7 +5012,7 @@
         <v>-126</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J59" s="21">
         <v>90</v>
@@ -5064,19 +5026,19 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F60" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G60" s="21">
@@ -5088,7 +5050,7 @@
         <v>-126</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J60" s="21">
         <v>180</v>
@@ -5102,36 +5064,36 @@
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="B62" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>181</v>
-      </c>
       <c r="D62" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F62" s="21">
         <v>0</v>
@@ -5140,11 +5102,11 @@
         <v>0</v>
       </c>
       <c r="H62" s="21">
-        <f>=PARAM!$D$6/2+PARAM!$E$15/2</f>
+        <f>=PARAM!$D$6/2+PARAM!$E$14/2</f>
         <v>156</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J62" s="21"/>
       <c r="K62" s="21"/>
@@ -5152,50 +5114,50 @@
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C64" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B64" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>183</v>
-      </c>
       <c r="D64" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F64" s="21">
         <v>0</v>
       </c>
       <c r="G64" s="21">
-        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
+        <f>=PARAM!$G$27/2+((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
         <v>77.5</v>
       </c>
       <c r="H64" s="21">
-        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2</f>
+        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15/2</f>
         <v>130</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J64" s="21"/>
       <c r="K64" s="21"/>
@@ -5203,30 +5165,30 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F65" s="21">
         <v>0</v>
       </c>
       <c r="G65" s="21">
-        <f>=-(PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2)</f>
+        <f>=-(PARAM!$G$27/2+((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2)</f>
         <v>-77.5</v>
       </c>
       <c r="H65" s="21">
-        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2</f>
+        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15/2</f>
         <v>130</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J65" s="21"/>
       <c r="K65" s="21"/>
@@ -5234,36 +5196,36 @@
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="D66" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="E66" s="21" t="s">
-        <v>184</v>
-      </c>
       <c r="F66" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B67" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>186</v>
-      </c>
       <c r="D67" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F67" s="21">
         <v>0</v>
@@ -5272,11 +5234,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="21">
-        <f>=-(PARAM!$D$6/2+PARAM!$E$15/2)</f>
+        <f>=-(PARAM!$D$6/2+PARAM!$E$14/2)</f>
         <v>-156</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J67" s="21"/>
       <c r="K67" s="21"/>
@@ -5284,50 +5246,50 @@
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B69" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>188</v>
-      </c>
       <c r="D69" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E69" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F69" s="21">
         <v>0</v>
       </c>
       <c r="G69" s="21">
-        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
+        <f>=PARAM!$G$27/2+((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
         <v>77.5</v>
       </c>
       <c r="H69" s="21">
-        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2)</f>
+        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15/2)</f>
         <v>-130</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J69" s="21"/>
       <c r="K69" s="21"/>
@@ -5335,30 +5297,30 @@
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F70" s="21">
         <v>0</v>
       </c>
       <c r="G70" s="21">
-        <f>=-(PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2)</f>
+        <f>=-(PARAM!$G$27/2+((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2)</f>
         <v>-77.5</v>
       </c>
       <c r="H70" s="21">
-        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2)</f>
+        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15/2)</f>
         <v>-130</v>
       </c>
       <c r="I70" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J70" s="21"/>
       <c r="K70" s="21"/>
@@ -5366,49 +5328,49 @@
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C71" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D71" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="E71" s="21" t="s">
-        <v>189</v>
-      </c>
       <c r="F71" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B72" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>191</v>
-      </c>
       <c r="D72" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F72" s="21">
         <v>0</v>
       </c>
       <c r="G72" s="21">
-        <f>=PARAM!$F$6/2+PARAM!$E$17/2</f>
+        <f>=PARAM!$F$6/2+PARAM!$E$16/2</f>
         <v>10</v>
       </c>
       <c r="H72" s="21">
         <v>0</v>
       </c>
       <c r="I72" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J72" s="21"/>
       <c r="K72" s="21"/>
@@ -5416,29 +5378,29 @@
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E73" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F73" s="21">
         <v>0</v>
       </c>
       <c r="G73" s="21">
-        <f>=-(PARAM!$F$6/2+PARAM!$E$17/2)</f>
+        <f>=-(PARAM!$F$6/2+PARAM!$E$16/2)</f>
         <v>-10</v>
       </c>
       <c r="H73" s="21">
         <v>0</v>
       </c>
       <c r="I73" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J73" s="21"/>
       <c r="K73" s="21"/>
@@ -5446,19 +5408,19 @@
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C74" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E74" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="D74" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>192</v>
-      </c>
       <c r="F74" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
@@ -5468,670 +5430,670 @@
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="B77" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>195</v>
-      </c>
       <c r="D77" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E77" s="21"/>
       <c r="F77" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="G77" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="H77" s="21">
+        <f>=(PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2-PARAM!$F$24/2</f>
+        <v>110</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J77" s="21">
+        <v>0</v>
+      </c>
+      <c r="K77" s="21">
+        <v>0</v>
+      </c>
+      <c r="L77" s="21">
+        <v>0</v>
+      </c>
+      <c r="M77" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N77" s="21">
+        <v>0</v>
+      </c>
+      <c r="O77" s="21">
+        <v>0</v>
+      </c>
+      <c r="P77" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q77" s="21">
+        <v>0</v>
+      </c>
+      <c r="R77" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S77" s="21">
+        <v>0</v>
+      </c>
+      <c r="T77" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B78" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="G78" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="H78" s="21">
+        <f>=(PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2-PARAM!$F$24/2</f>
+        <v>110</v>
+      </c>
+      <c r="I78" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J78" s="21">
+        <v>0</v>
+      </c>
+      <c r="K78" s="21">
+        <v>0</v>
+      </c>
+      <c r="L78" s="21">
+        <v>0</v>
+      </c>
+      <c r="M78" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N78" s="21">
+        <v>0</v>
+      </c>
+      <c r="O78" s="21">
+        <v>0</v>
+      </c>
+      <c r="P78" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q78" s="21">
+        <v>0</v>
+      </c>
+      <c r="R78" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S78" s="21">
+        <v>0</v>
+      </c>
+      <c r="T78" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B79" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="G79" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="H79" s="21">
+        <f>=(PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2-PARAM!$F$24/2</f>
+        <v>110</v>
+      </c>
+      <c r="I79" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J79" s="21">
+        <v>0</v>
+      </c>
+      <c r="K79" s="21">
+        <v>0</v>
+      </c>
+      <c r="L79" s="21">
+        <v>0</v>
+      </c>
+      <c r="M79" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N79" s="21">
+        <v>0</v>
+      </c>
+      <c r="O79" s="21">
+        <v>0</v>
+      </c>
+      <c r="P79" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q79" s="21">
+        <v>0</v>
+      </c>
+      <c r="R79" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S79" s="21">
+        <v>0</v>
+      </c>
+      <c r="T79" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B80" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="G80" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="H80" s="21">
+        <f>=(PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2-PARAM!$F$24/2</f>
+        <v>110</v>
+      </c>
+      <c r="I80" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J80" s="21">
+        <v>0</v>
+      </c>
+      <c r="K80" s="21">
+        <v>0</v>
+      </c>
+      <c r="L80" s="21">
+        <v>0</v>
+      </c>
+      <c r="M80" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N80" s="21">
+        <v>0</v>
+      </c>
+      <c r="O80" s="21">
+        <v>0</v>
+      </c>
+      <c r="P80" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q80" s="21">
+        <v>0</v>
+      </c>
+      <c r="R80" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S80" s="21">
+        <v>0</v>
+      </c>
+      <c r="T80" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B81" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="G81" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="H81" s="21">
+        <f>=-((PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2)-PARAM!$F$24/2</f>
+        <v>-177</v>
+      </c>
+      <c r="I81" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J81" s="21">
+        <v>0</v>
+      </c>
+      <c r="K81" s="21">
+        <v>0</v>
+      </c>
+      <c r="L81" s="21">
+        <v>0</v>
+      </c>
+      <c r="M81" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N81" s="21">
+        <v>0</v>
+      </c>
+      <c r="O81" s="21">
+        <v>0</v>
+      </c>
+      <c r="P81" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q81" s="21">
+        <v>0</v>
+      </c>
+      <c r="R81" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S81" s="21">
+        <v>0</v>
+      </c>
+      <c r="T81" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B82" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21">
+        <f>=(PARAM!$D$27/2)</f>
+        <v>35</v>
+      </c>
+      <c r="G82" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="H82" s="21">
+        <f>=-((PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2)-PARAM!$F$24/2</f>
+        <v>-177</v>
+      </c>
+      <c r="I82" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J82" s="21">
+        <v>0</v>
+      </c>
+      <c r="K82" s="21">
+        <v>0</v>
+      </c>
+      <c r="L82" s="21">
+        <v>0</v>
+      </c>
+      <c r="M82" s="21">
+        <f>=((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>75</v>
+      </c>
+      <c r="N82" s="21">
+        <v>0</v>
+      </c>
+      <c r="O82" s="21">
+        <v>0</v>
+      </c>
+      <c r="P82" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q82" s="21">
+        <v>0</v>
+      </c>
+      <c r="R82" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S82" s="21">
+        <v>0</v>
+      </c>
+      <c r="T82" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B83" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="G83" s="21">
+        <f>=(PARAM!$G$27/2)</f>
+        <v>50</v>
+      </c>
+      <c r="H83" s="21">
+        <f>=-((PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2)-PARAM!$F$24/2</f>
+        <v>-177</v>
+      </c>
+      <c r="I83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J83" s="21">
+        <v>0</v>
+      </c>
+      <c r="K83" s="21">
+        <v>0</v>
+      </c>
+      <c r="L83" s="21">
+        <v>0</v>
+      </c>
+      <c r="M83" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N83" s="21">
+        <v>0</v>
+      </c>
+      <c r="O83" s="21">
+        <v>0</v>
+      </c>
+      <c r="P83" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q83" s="21">
+        <v>0</v>
+      </c>
+      <c r="R83" s="21">
+        <f>=((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>55</v>
+      </c>
+      <c r="S83" s="21">
+        <v>0</v>
+      </c>
+      <c r="T83" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B84" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21">
+        <f>=-(PARAM!$D$27/2)</f>
+        <v>-35</v>
+      </c>
+      <c r="G84" s="21">
+        <f>=-(PARAM!$G$27/2)</f>
+        <v>-50</v>
+      </c>
+      <c r="H84" s="21">
+        <f>=-((PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2)-PARAM!$F$24/2</f>
+        <v>-177</v>
+      </c>
+      <c r="I84" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J84" s="21">
+        <v>0</v>
+      </c>
+      <c r="K84" s="21">
+        <v>0</v>
+      </c>
+      <c r="L84" s="21">
+        <v>0</v>
+      </c>
+      <c r="M84" s="21">
+        <f>=-((PARAM!$D$14/2-PARAM!$E$27-PARAM!$D$27/2)/(PARAM!$C$27/2-1))</f>
+        <v>-75</v>
+      </c>
+      <c r="N84" s="21">
+        <v>0</v>
+      </c>
+      <c r="O84" s="21">
+        <v>0</v>
+      </c>
+      <c r="P84" s="21">
+        <f>=PARAM!$C$27/2-1</f>
+        <v>1</v>
+      </c>
+      <c r="Q84" s="21">
+        <v>0</v>
+      </c>
+      <c r="R84" s="21">
+        <f>=-((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))</f>
+        <v>-55</v>
+      </c>
+      <c r="S84" s="21">
+        <v>0</v>
+      </c>
+      <c r="T84" s="21">
+        <f>=PARAM!$F$27/2-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E85" s="21"/>
+      <c r="F85" s="21">
         <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G77" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H77" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I77" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G85" s="21">
+        <f>=PARAM!$G$24/2</f>
+        <v>30</v>
+      </c>
+      <c r="H85" s="21">
+        <f>=-(PARAM!$C$16/2-PARAM!$H$28)</f>
+        <v>-70</v>
+      </c>
+      <c r="I85" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="J77" s="21">
-        <v>0</v>
-      </c>
-      <c r="K77" s="21">
-        <v>0</v>
-      </c>
-      <c r="L77" s="21">
-        <v>0</v>
-      </c>
-      <c r="M77" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="N77" s="21">
-        <v>0</v>
-      </c>
-      <c r="O77" s="21">
-        <v>0</v>
-      </c>
-      <c r="P77" s="21">
+      <c r="J85" s="21">
+        <v>0</v>
+      </c>
+      <c r="K85" s="21">
+        <v>0</v>
+      </c>
+      <c r="L85" s="21">
+        <v>0</v>
+      </c>
+      <c r="M85" s="21">
+        <f>=((PARAM!$D$16/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>70</v>
+      </c>
+      <c r="N85" s="21">
+        <v>0</v>
+      </c>
+      <c r="O85" s="21">
+        <v>0</v>
+      </c>
+      <c r="P85" s="21">
         <f>=PARAM!$C$28/2-1</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="21">
-        <v>0</v>
-      </c>
-      <c r="R77" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="S77" s="21">
-        <v>0</v>
-      </c>
-      <c r="T77" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B78" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G78" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H78" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I78" s="21" t="s">
+      <c r="Q85" s="21">
+        <v>0</v>
+      </c>
+      <c r="R85" s="21">
+        <v>0</v>
+      </c>
+      <c r="S85" s="21">
+        <f>=(PARAM!$C$16-2*PARAM!$H$28-PARAM!$G$28)/(PARAM!$F$28-1)</f>
+        <v>70</v>
+      </c>
+      <c r="T85" s="21">
+        <f>=PARAM!$F$28-1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B86" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E86" s="21"/>
+      <c r="F86" s="21">
+        <f>=-(PARAM!$D$28/2)</f>
+        <v>-30</v>
+      </c>
+      <c r="G86" s="21">
+        <f>=PARAM!$G$24/2</f>
+        <v>30</v>
+      </c>
+      <c r="H86" s="21">
+        <f>=-(PARAM!$C$16/2-PARAM!$H$28)</f>
+        <v>-70</v>
+      </c>
+      <c r="I86" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="J78" s="21">
-        <v>0</v>
-      </c>
-      <c r="K78" s="21">
-        <v>0</v>
-      </c>
-      <c r="L78" s="21">
-        <v>0</v>
-      </c>
-      <c r="M78" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="N78" s="21">
-        <v>0</v>
-      </c>
-      <c r="O78" s="21">
-        <v>0</v>
-      </c>
-      <c r="P78" s="21">
+      <c r="J86" s="21">
+        <v>0</v>
+      </c>
+      <c r="K86" s="21">
+        <v>0</v>
+      </c>
+      <c r="L86" s="21">
+        <v>0</v>
+      </c>
+      <c r="M86" s="21">
+        <f>=-((PARAM!$D$16/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
+        <v>-70</v>
+      </c>
+      <c r="N86" s="21">
+        <v>0</v>
+      </c>
+      <c r="O86" s="21">
+        <v>0</v>
+      </c>
+      <c r="P86" s="21">
         <f>=PARAM!$C$28/2-1</f>
         <v>1</v>
       </c>
-      <c r="Q78" s="21">
-        <v>0</v>
-      </c>
-      <c r="R78" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="S78" s="21">
-        <v>0</v>
-      </c>
-      <c r="T78" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B79" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C79" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D79" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G79" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H79" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I79" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J79" s="21">
-        <v>0</v>
-      </c>
-      <c r="K79" s="21">
-        <v>0</v>
-      </c>
-      <c r="L79" s="21">
-        <v>0</v>
-      </c>
-      <c r="M79" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="N79" s="21">
-        <v>0</v>
-      </c>
-      <c r="O79" s="21">
-        <v>0</v>
-      </c>
-      <c r="P79" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q79" s="21">
-        <v>0</v>
-      </c>
-      <c r="R79" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="S79" s="21">
-        <v>0</v>
-      </c>
-      <c r="T79" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B80" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E80" s="21"/>
-      <c r="F80" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G80" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H80" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
-        <v>110</v>
-      </c>
-      <c r="I80" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J80" s="21">
-        <v>0</v>
-      </c>
-      <c r="K80" s="21">
-        <v>0</v>
-      </c>
-      <c r="L80" s="21">
-        <v>0</v>
-      </c>
-      <c r="M80" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="N80" s="21">
-        <v>0</v>
-      </c>
-      <c r="O80" s="21">
-        <v>0</v>
-      </c>
-      <c r="P80" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q80" s="21">
-        <v>0</v>
-      </c>
-      <c r="R80" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="S80" s="21">
-        <v>0</v>
-      </c>
-      <c r="T80" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B81" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G81" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H81" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I81" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J81" s="21">
-        <v>0</v>
-      </c>
-      <c r="K81" s="21">
-        <v>0</v>
-      </c>
-      <c r="L81" s="21">
-        <v>0</v>
-      </c>
-      <c r="M81" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="N81" s="21">
-        <v>0</v>
-      </c>
-      <c r="O81" s="21">
-        <v>0</v>
-      </c>
-      <c r="P81" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q81" s="21">
-        <v>0</v>
-      </c>
-      <c r="R81" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="S81" s="21">
-        <v>0</v>
-      </c>
-      <c r="T81" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B82" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21">
-        <f>=(PARAM!$D$28/2)</f>
-        <v>35</v>
-      </c>
-      <c r="G82" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H82" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I82" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J82" s="21">
-        <v>0</v>
-      </c>
-      <c r="K82" s="21">
-        <v>0</v>
-      </c>
-      <c r="L82" s="21">
-        <v>0</v>
-      </c>
-      <c r="M82" s="21">
-        <f>=((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>75</v>
-      </c>
-      <c r="N82" s="21">
-        <v>0</v>
-      </c>
-      <c r="O82" s="21">
-        <v>0</v>
-      </c>
-      <c r="P82" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q82" s="21">
-        <v>0</v>
-      </c>
-      <c r="R82" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="S82" s="21">
-        <v>0</v>
-      </c>
-      <c r="T82" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B83" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G83" s="21">
-        <f>=(PARAM!$G$28/2)</f>
-        <v>50</v>
-      </c>
-      <c r="H83" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I83" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J83" s="21">
-        <v>0</v>
-      </c>
-      <c r="K83" s="21">
-        <v>0</v>
-      </c>
-      <c r="L83" s="21">
-        <v>0</v>
-      </c>
-      <c r="M83" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="N83" s="21">
-        <v>0</v>
-      </c>
-      <c r="O83" s="21">
-        <v>0</v>
-      </c>
-      <c r="P83" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q83" s="21">
-        <v>0</v>
-      </c>
-      <c r="R83" s="21">
-        <f>=((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>55</v>
-      </c>
-      <c r="S83" s="21">
-        <v>0</v>
-      </c>
-      <c r="T83" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B84" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21">
-        <f>=-(PARAM!$D$28/2)</f>
-        <v>-35</v>
-      </c>
-      <c r="G84" s="21">
-        <f>=-(PARAM!$G$28/2)</f>
-        <v>-50</v>
-      </c>
-      <c r="H84" s="21">
-        <f>=-((PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2)-PARAM!$F$25/2</f>
-        <v>-177</v>
-      </c>
-      <c r="I84" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J84" s="21">
-        <v>0</v>
-      </c>
-      <c r="K84" s="21">
-        <v>0</v>
-      </c>
-      <c r="L84" s="21">
-        <v>0</v>
-      </c>
-      <c r="M84" s="21">
-        <f>=-((PARAM!$D$15/2-PARAM!$E$28-PARAM!$D$28/2)/(PARAM!$C$28/2-1))</f>
-        <v>-75</v>
-      </c>
-      <c r="N84" s="21">
-        <v>0</v>
-      </c>
-      <c r="O84" s="21">
-        <v>0</v>
-      </c>
-      <c r="P84" s="21">
-        <f>=PARAM!$C$28/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q84" s="21">
-        <v>0</v>
-      </c>
-      <c r="R84" s="21">
-        <f>=-((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))</f>
-        <v>-55</v>
-      </c>
-      <c r="S84" s="21">
-        <v>0</v>
-      </c>
-      <c r="T84" s="21">
-        <f>=PARAM!$F$28/2-1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B85" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D85" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21">
-        <f>=(PARAM!$D$29/2)</f>
-        <v>30</v>
-      </c>
-      <c r="G85" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H85" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="I85" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="J85" s="21">
-        <v>0</v>
-      </c>
-      <c r="K85" s="21">
-        <v>0</v>
-      </c>
-      <c r="L85" s="21">
-        <v>0</v>
-      </c>
-      <c r="M85" s="21">
-        <f>=((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
+      <c r="Q86" s="21">
+        <v>0</v>
+      </c>
+      <c r="R86" s="21">
+        <v>0</v>
+      </c>
+      <c r="S86" s="21">
+        <f>=(PARAM!$C$16-2*PARAM!$H$28-PARAM!$G$28)/(PARAM!$F$28-1)</f>
         <v>70</v>
       </c>
-      <c r="N85" s="21">
-        <v>0</v>
-      </c>
-      <c r="O85" s="21">
-        <v>0</v>
-      </c>
-      <c r="P85" s="21">
-        <f>=PARAM!$C$29/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q85" s="21">
-        <v>0</v>
-      </c>
-      <c r="R85" s="21">
-        <v>0</v>
-      </c>
-      <c r="S85" s="21">
-        <f>=(PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1)</f>
-        <v>70</v>
-      </c>
-      <c r="T85" s="21">
-        <f>=PARAM!$F$29-1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B86" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D86" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E86" s="21"/>
-      <c r="F86" s="21">
-        <f>=-(PARAM!$D$29/2)</f>
-        <v>-30</v>
-      </c>
-      <c r="G86" s="21">
-        <f>=PARAM!$G$25/2</f>
-        <v>30</v>
-      </c>
-      <c r="H86" s="21">
-        <f>=-(PARAM!$C$17/2-PARAM!$H$29)</f>
-        <v>-70</v>
-      </c>
-      <c r="I86" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="J86" s="21">
-        <v>0</v>
-      </c>
-      <c r="K86" s="21">
-        <v>0</v>
-      </c>
-      <c r="L86" s="21">
-        <v>0</v>
-      </c>
-      <c r="M86" s="21">
-        <f>=-((PARAM!$D$17/2-PARAM!$E$29-PARAM!$D$29/2)/(PARAM!$C$29/2-1))</f>
-        <v>-70</v>
-      </c>
-      <c r="N86" s="21">
-        <v>0</v>
-      </c>
-      <c r="O86" s="21">
-        <v>0</v>
-      </c>
-      <c r="P86" s="21">
-        <f>=PARAM!$C$29/2-1</f>
-        <v>1</v>
-      </c>
-      <c r="Q86" s="21">
-        <v>0</v>
-      </c>
-      <c r="R86" s="21">
-        <v>0</v>
-      </c>
-      <c r="S86" s="21">
-        <f>=(PARAM!$C$17-2*PARAM!$H$29-PARAM!$G$29)/(PARAM!$F$29-1)</f>
-        <v>70</v>
-      </c>
       <c r="T86" s="21">
-        <f>=PARAM!$F$29-1</f>
+        <f>=PARAM!$F$28-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E87" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
@@ -6141,24 +6103,24 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B90" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C90" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C90" s="21" t="s">
+      <c r="D90" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="E90" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D90" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="E90" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F90" s="21">
-        <f>=-(PARAM!$C$8/2+PARAM!$J$6/2)</f>
+        <f>=-(PARAM!$C$7/2+PARAM!$J$6/2)</f>
         <v>-460</v>
       </c>
       <c r="G90" s="21">
@@ -6171,19 +6133,19 @@
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B91" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C91" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C91" s="21" t="s">
+      <c r="D91" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="E91" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D91" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="E91" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F91" s="21">
-        <f>=PARAM!$C$8/2+PARAM!$J$6/2</f>
+        <f>=PARAM!$C$7/2+PARAM!$J$6/2</f>
         <v>460</v>
       </c>
       <c r="G91" s="21">
@@ -6196,17 +6158,17 @@
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B92" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C92" s="21" t="s">
+      <c r="D92" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E92" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D92" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="E92" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F92" s="21">
         <v>0</v>
       </c>
@@ -6214,48 +6176,48 @@
         <v>0</v>
       </c>
       <c r="H92" s="21">
-        <f>=PARAM!$D$6/2+PARAM!$E$15/2</f>
+        <f>=PARAM!$D$6/2+PARAM!$E$14/2</f>
         <v>156</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B93" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C93" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C93" s="21" t="s">
+      <c r="D93" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E93" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D93" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="E93" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F93" s="21">
         <v>0</v>
       </c>
       <c r="G93" s="21">
-        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
+        <f>=PARAM!$G$27/2+((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
         <v>77.5</v>
       </c>
       <c r="H93" s="21">
-        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2</f>
+        <f>=PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15/2</f>
         <v>130</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C94" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C94" s="21" t="s">
+      <c r="D94" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E94" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D94" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F94" s="21">
         <v>0</v>
       </c>
@@ -6263,53 +6225,53 @@
         <v>0</v>
       </c>
       <c r="H94" s="21">
-        <f>=-(PARAM!$D$6/2+PARAM!$E$15/2)</f>
+        <f>=-(PARAM!$D$6/2+PARAM!$E$14/2)</f>
         <v>-156</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C95" s="21" t="s">
+      <c r="D95" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="E95" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D95" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E95" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F95" s="21">
         <v>0</v>
       </c>
       <c r="G95" s="21">
-        <f>=PARAM!$G$28/2+((PARAM!$C$15/2-PARAM!$H$28-PARAM!$G$28/2)/(PARAM!$F$28/2-1))/2</f>
+        <f>=PARAM!$G$27/2+((PARAM!$C$14/2-PARAM!$H$27-PARAM!$G$27/2)/(PARAM!$F$27/2-1))/2</f>
         <v>77.5</v>
       </c>
       <c r="H95" s="21">
-        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16/2)</f>
+        <f>=-(PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15/2)</f>
         <v>-130</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B96" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C96" s="21" t="s">
+      <c r="D96" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E96" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D96" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="E96" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F96" s="21">
         <v>0</v>
       </c>
       <c r="G96" s="21">
-        <f>=PARAM!$F$6/2+PARAM!$E$17/2</f>
+        <f>=PARAM!$F$6/2+PARAM!$E$16/2</f>
         <v>10</v>
       </c>
       <c r="H96" s="21">
@@ -6318,27 +6280,27 @@
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C97" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C97" s="21" t="s">
+      <c r="D97" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="E97" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D97" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E97" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="F97" s="21">
-        <f>=(PARAM!$D$28/2)</f>
+        <f>=(PARAM!$D$27/2)</f>
         <v>35</v>
       </c>
       <c r="G97" s="21">
-        <f>=(PARAM!$G$28/2)</f>
+        <f>=(PARAM!$G$27/2)</f>
         <v>50</v>
       </c>
       <c r="H97" s="21">
-        <f>=(PARAM!$D$6/2+PARAM!$E$15+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$16)/2-PARAM!$F$25/2</f>
+        <f>=(PARAM!$D$6/2+PARAM!$E$14+PARAM!$D$6/2-PARAM!$G$6-PARAM!$E$15)/2-PARAM!$F$24/2</f>
         <v>110</v>
       </c>
     </row>
@@ -6349,77 +6311,77 @@
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D100" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="C100" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D100" s="21" t="s">
+      <c r="E100" s="21" t="s">
         <v>204</v>
-      </c>
-      <c r="E100" s="21" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D101" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E101" s="21" t="s">
         <v>206</v>
-      </c>
-      <c r="E101" s="21" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D103" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="C103" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D103" s="21" t="s">
-        <v>204</v>
-      </c>
       <c r="E103" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D104" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E104" s="21" t="s">
         <v>210</v>
-      </c>
-      <c r="E104" s="21" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
@@ -6429,7 +6391,7 @@
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_SPLICE.xlsx
+++ b/plate3d/PLATE3D_SPLICE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="216">
   <si>
     <t>Section</t>
   </si>
@@ -646,6 +646,18 @@
   </si>
   <si>
     <t>WEB - SIDE</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -2717,7 +2729,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3250,14 +3262,14 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T106"/>
+  <dimension ref="A1:T107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -3266,12 +3278,12 @@
     <col min="4" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>120</v>
       </c>
@@ -3279,7 +3291,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>69</v>
       </c>
@@ -3326,12 +3338,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>129</v>
       </c>
@@ -3633,12 +3645,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>150</v>
       </c>
@@ -3687,12 +3699,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>157</v>
       </c>
@@ -3741,7 +3753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
         <v>159</v>
       </c>
@@ -3782,7 +3794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B25" s="20" t="s">
         <v>159</v>
       </c>
@@ -3823,7 +3835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
         <v>159</v>
       </c>
@@ -3908,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
         <v>159</v>
       </c>
@@ -3949,7 +3961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B29" s="20" t="s">
         <v>159</v>
       </c>
@@ -3990,7 +4002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
         <v>159</v>
       </c>
@@ -4074,7 +4086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
         <v>159</v>
       </c>
@@ -4157,7 +4169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
         <v>159</v>
       </c>
@@ -4241,7 +4253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
         <v>159</v>
       </c>
@@ -4326,7 +4338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
         <v>159</v>
       </c>
@@ -4411,7 +4423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B40" s="20" t="s">
         <v>159</v>
       </c>
@@ -4518,17 +4530,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
         <v>169</v>
       </c>
@@ -4567,7 +4579,7 @@
       <c r="K46" s="21"/>
       <c r="L46" s="21"/>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
         <v>171</v>
       </c>
@@ -4598,7 +4610,7 @@
       <c r="K47" s="21"/>
       <c r="L47" s="21"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
         <v>171</v>
       </c>
@@ -4628,7 +4640,7 @@
       <c r="K48" s="21"/>
       <c r="L48" s="21"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B49" s="20" t="s">
         <v>171</v>
       </c>
@@ -4666,7 +4678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B50" s="20" t="s">
         <v>171</v>
       </c>
@@ -4704,7 +4716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B51" s="20" t="s">
         <v>171</v>
       </c>
@@ -4742,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52" s="20" t="s">
         <v>171</v>
       </c>
@@ -4780,7 +4792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="s">
         <v>171</v>
       </c>
@@ -4837,7 +4849,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B55" s="20" t="s">
         <v>171</v>
       </c>
@@ -4874,7 +4886,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B56" s="20" t="s">
         <v>171</v>
       </c>
@@ -4910,7 +4922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
         <v>171</v>
       </c>
@@ -4948,7 +4960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B58" s="20" t="s">
         <v>171</v>
       </c>
@@ -4986,7 +4998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
         <v>171</v>
       </c>
@@ -5024,7 +5036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
         <v>171</v>
       </c>
@@ -5062,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
         <v>171</v>
       </c>
@@ -5112,7 +5124,7 @@
       <c r="K62" s="21"/>
       <c r="L62" s="21"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
         <v>171</v>
       </c>
@@ -5163,7 +5175,7 @@
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
         <v>171</v>
       </c>
@@ -5194,7 +5206,7 @@
       <c r="K65" s="21"/>
       <c r="L65" s="21"/>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
         <v>171</v>
       </c>
@@ -5244,7 +5256,7 @@
       <c r="K67" s="21"/>
       <c r="L67" s="21"/>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
         <v>171</v>
       </c>
@@ -5295,7 +5307,7 @@
       <c r="K69" s="21"/>
       <c r="L69" s="21"/>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
         <v>171</v>
       </c>
@@ -5326,7 +5338,7 @@
       <c r="K70" s="21"/>
       <c r="L70" s="21"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
         <v>171</v>
       </c>
@@ -5376,7 +5388,7 @@
       <c r="K72" s="21"/>
       <c r="L72" s="21"/>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
         <v>171</v>
       </c>
@@ -5406,7 +5418,7 @@
       <c r="K73" s="21"/>
       <c r="L73" s="21"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B74" s="20" t="s">
         <v>171</v>
       </c>
@@ -5423,12 +5435,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
         <v>192</v>
       </c>
@@ -5500,7 +5512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B78" s="20" t="s">
         <v>171</v>
       </c>
@@ -5564,7 +5576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
         <v>171</v>
       </c>
@@ -5628,7 +5640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B80" s="20" t="s">
         <v>171</v>
       </c>
@@ -5692,7 +5704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B81" s="20" t="s">
         <v>171</v>
       </c>
@@ -5756,7 +5768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B82" s="20" t="s">
         <v>171</v>
       </c>
@@ -5820,7 +5832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B83" s="20" t="s">
         <v>171</v>
       </c>
@@ -5884,7 +5896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B84" s="20" t="s">
         <v>171</v>
       </c>
@@ -6015,7 +6027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B86" s="20" t="s">
         <v>171</v>
       </c>
@@ -6079,7 +6091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B87" s="20" t="s">
         <v>171</v>
       </c>
@@ -6096,17 +6108,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B90" s="20" t="s">
         <v>198</v>
       </c>
@@ -6131,7 +6143,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B91" s="20" t="s">
         <v>198</v>
       </c>
@@ -6156,7 +6168,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B92" s="20" t="s">
         <v>198</v>
       </c>
@@ -6180,7 +6192,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B93" s="20" t="s">
         <v>198</v>
       </c>
@@ -6205,7 +6217,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
         <v>198</v>
       </c>
@@ -6229,7 +6241,7 @@
         <v>-156</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
         <v>198</v>
       </c>
@@ -6254,7 +6266,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B96" s="20" t="s">
         <v>198</v>
       </c>
@@ -6278,7 +6290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
         <v>198</v>
       </c>
@@ -6304,17 +6316,17 @@
         <v>110</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
         <v>202</v>
       </c>
@@ -6324,11 +6336,15 @@
       <c r="D100" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E100" s="21" t="s">
+      <c r="E100" s="21"/>
+      <c r="G100">
+        <v>10</v>
+      </c>
+      <c r="H100" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
         <v>202</v>
       </c>
@@ -6338,11 +6354,15 @@
       <c r="D101" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="E101" s="21" t="s">
+      <c r="E101" s="21"/>
+      <c r="G101">
+        <v>10</v>
+      </c>
+      <c r="H101" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B102" s="20" t="s">
         <v>202</v>
       </c>
@@ -6352,11 +6372,15 @@
       <c r="D102" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="E102" s="21" t="s">
+      <c r="E102" s="21"/>
+      <c r="G102">
+        <v>10</v>
+      </c>
+      <c r="H102" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B103" s="20" t="s">
         <v>202</v>
       </c>
@@ -6366,11 +6390,15 @@
       <c r="D103" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E103" s="21" t="s">
+      <c r="E103" s="21"/>
+      <c r="G103">
+        <v>10</v>
+      </c>
+      <c r="H103" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B104" s="20" t="s">
         <v>202</v>
       </c>
@@ -6380,22 +6408,43 @@
       <c r="D104" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="E104" s="21" t="s">
+      <c r="E104" s="21"/>
+      <c r="G104">
+        <v>10</v>
+      </c>
+      <c r="H104" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B106" s="20" t="s">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
         <v>211</v>
+      </c>
+      <c r="C106" t="s">
+        <v>212</v>
+      </c>
+      <c r="D106" t="s">
+        <v>213</v>
+      </c>
+      <c r="E106">
+        <v>10</v>
+      </c>
+      <c r="F106" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="20" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_SPLICE.xlsx
+++ b/plate3d/PLATE3D_SPLICE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="212">
   <si>
     <t>Section</t>
   </si>
@@ -646,18 +646,6 @@
   </si>
   <si>
     <t>WEB - SIDE</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -2729,7 +2717,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -3262,14 +3250,14 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T107"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -3278,12 +3266,12 @@
     <col min="4" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>120</v>
       </c>
@@ -3291,7 +3279,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>69</v>
       </c>
@@ -3338,12 +3326,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>129</v>
       </c>
@@ -3645,12 +3633,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>150</v>
       </c>
@@ -3699,12 +3687,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>157</v>
       </c>
@@ -3753,7 +3741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
         <v>159</v>
       </c>
@@ -3794,7 +3782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="20" t="s">
         <v>159</v>
       </c>
@@ -3835,7 +3823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
         <v>159</v>
       </c>
@@ -3920,7 +3908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
         <v>159</v>
       </c>
@@ -3961,7 +3949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="20" t="s">
         <v>159</v>
       </c>
@@ -4002,7 +3990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
         <v>159</v>
       </c>
@@ -4086,7 +4074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
         <v>159</v>
       </c>
@@ -4169,7 +4157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
         <v>159</v>
       </c>
@@ -4253,7 +4241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
         <v>159</v>
       </c>
@@ -4338,7 +4326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
         <v>159</v>
       </c>
@@ -4423,7 +4411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="20" t="s">
         <v>159</v>
       </c>
@@ -4530,17 +4518,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
         <v>169</v>
       </c>
@@ -4579,7 +4567,7 @@
       <c r="K46" s="21"/>
       <c r="L46" s="21"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
         <v>171</v>
       </c>
@@ -4610,7 +4598,7 @@
       <c r="K47" s="21"/>
       <c r="L47" s="21"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
         <v>171</v>
       </c>
@@ -4640,7 +4628,7 @@
       <c r="K48" s="21"/>
       <c r="L48" s="21"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="20" t="s">
         <v>171</v>
       </c>
@@ -4678,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="20" t="s">
         <v>171</v>
       </c>
@@ -4716,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="20" t="s">
         <v>171</v>
       </c>
@@ -4754,7 +4742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="20" t="s">
         <v>171</v>
       </c>
@@ -4792,7 +4780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="s">
         <v>171</v>
       </c>
@@ -4849,7 +4837,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="20" t="s">
         <v>171</v>
       </c>
@@ -4886,7 +4874,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="20" t="s">
         <v>171</v>
       </c>
@@ -4922,7 +4910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
         <v>171</v>
       </c>
@@ -4960,7 +4948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" s="20" t="s">
         <v>171</v>
       </c>
@@ -4998,7 +4986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
         <v>171</v>
       </c>
@@ -5036,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
         <v>171</v>
       </c>
@@ -5074,7 +5062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
         <v>171</v>
       </c>
@@ -5124,7 +5112,7 @@
       <c r="K62" s="21"/>
       <c r="L62" s="21"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
         <v>171</v>
       </c>
@@ -5175,7 +5163,7 @@
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
         <v>171</v>
       </c>
@@ -5206,7 +5194,7 @@
       <c r="K65" s="21"/>
       <c r="L65" s="21"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
         <v>171</v>
       </c>
@@ -5256,7 +5244,7 @@
       <c r="K67" s="21"/>
       <c r="L67" s="21"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
         <v>171</v>
       </c>
@@ -5307,7 +5295,7 @@
       <c r="K69" s="21"/>
       <c r="L69" s="21"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
         <v>171</v>
       </c>
@@ -5338,7 +5326,7 @@
       <c r="K70" s="21"/>
       <c r="L70" s="21"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
         <v>171</v>
       </c>
@@ -5388,7 +5376,7 @@
       <c r="K72" s="21"/>
       <c r="L72" s="21"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
         <v>171</v>
       </c>
@@ -5418,7 +5406,7 @@
       <c r="K73" s="21"/>
       <c r="L73" s="21"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" s="20" t="s">
         <v>171</v>
       </c>
@@ -5435,12 +5423,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
         <v>192</v>
       </c>
@@ -5512,7 +5500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B78" s="20" t="s">
         <v>171</v>
       </c>
@@ -5576,7 +5564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
         <v>171</v>
       </c>
@@ -5640,7 +5628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B80" s="20" t="s">
         <v>171</v>
       </c>
@@ -5704,7 +5692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="20" t="s">
         <v>171</v>
       </c>
@@ -5768,7 +5756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="20" t="s">
         <v>171</v>
       </c>
@@ -5832,7 +5820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B83" s="20" t="s">
         <v>171</v>
       </c>
@@ -5896,7 +5884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B84" s="20" t="s">
         <v>171</v>
       </c>
@@ -6027,7 +6015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B86" s="20" t="s">
         <v>171</v>
       </c>
@@ -6091,7 +6079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="20" t="s">
         <v>171</v>
       </c>
@@ -6108,17 +6096,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B90" s="20" t="s">
         <v>198</v>
       </c>
@@ -6143,7 +6131,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B91" s="20" t="s">
         <v>198</v>
       </c>
@@ -6168,7 +6156,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B92" s="20" t="s">
         <v>198</v>
       </c>
@@ -6192,7 +6180,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B93" s="20" t="s">
         <v>198</v>
       </c>
@@ -6217,7 +6205,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
         <v>198</v>
       </c>
@@ -6241,7 +6229,7 @@
         <v>-156</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
         <v>198</v>
       </c>
@@ -6266,7 +6254,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B96" s="20" t="s">
         <v>198</v>
       </c>
@@ -6290,7 +6278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
         <v>198</v>
       </c>
@@ -6316,17 +6304,17 @@
         <v>110</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
         <v>202</v>
       </c>
@@ -6336,15 +6324,11 @@
       <c r="D100" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E100" s="21"/>
-      <c r="G100">
-        <v>10</v>
-      </c>
-      <c r="H100" t="s">
+      <c r="E100" s="21" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
         <v>202</v>
       </c>
@@ -6354,15 +6338,11 @@
       <c r="D101" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="E101" s="21"/>
-      <c r="G101">
-        <v>10</v>
-      </c>
-      <c r="H101" t="s">
+      <c r="E101" s="21" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102" s="20" t="s">
         <v>202</v>
       </c>
@@ -6372,15 +6352,11 @@
       <c r="D102" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="E102" s="21"/>
-      <c r="G102">
-        <v>10</v>
-      </c>
-      <c r="H102" t="s">
+      <c r="E102" s="21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103" s="20" t="s">
         <v>202</v>
       </c>
@@ -6390,15 +6366,11 @@
       <c r="D103" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E103" s="21"/>
-      <c r="G103">
-        <v>10</v>
-      </c>
-      <c r="H103" t="s">
+      <c r="E103" s="21" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" s="20" t="s">
         <v>202</v>
       </c>
@@ -6408,43 +6380,22 @@
       <c r="D104" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="E104" s="21"/>
-      <c r="G104">
-        <v>10</v>
-      </c>
-      <c r="H104" t="s">
+      <c r="E104" s="21" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B106" t="s">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="20" t="s">
         <v>211</v>
-      </c>
-      <c r="C106" t="s">
-        <v>212</v>
-      </c>
-      <c r="D106" t="s">
-        <v>213</v>
-      </c>
-      <c r="E106">
-        <v>10</v>
-      </c>
-      <c r="F106" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B107" s="20" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>